--- a/data/trans_orig/IP32-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78945</t>
+          <t>78421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87518</t>
+          <t>87296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>74260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>82864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156090</t>
+          <t>156731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168506</t>
+          <t>168349</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46922</t>
+          <t>45142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27058</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33101</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53600</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>366916</t>
+          <t>367145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>385124</t>
+          <t>386012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>423699</t>
+          <t>421942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>442007</t>
+          <t>443230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>796358</t>
+          <t>797273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>823508</t>
+          <t>823243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147129</t>
+          <t>145769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>159768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123921</t>
+          <t>124304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139183</t>
+          <t>139003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276539</t>
+          <t>275352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296077</t>
+          <t>296966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>53586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>78284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>61271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87207</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>602637</t>
+          <t>601674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>625959</t>
+          <t>626517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>632812</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>659522</t>
+          <t>658334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1242459</t>
+          <t>1243199</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1278423</t>
+          <t>1278122</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88202</t>
+          <t>88080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73025</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82811</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155013</t>
+          <t>154285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168750</t>
+          <t>168240</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43278</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>421151</t>
+          <t>420237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>437486</t>
+          <t>437447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>461232</t>
+          <t>462104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480122</t>
+          <t>479784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>889300</t>
+          <t>888435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>913261</t>
+          <t>912817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153311</t>
+          <t>153775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163262</t>
+          <t>163140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157026</t>
+          <t>156415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167374</t>
+          <t>167624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>313008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328948</t>
+          <t>328780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>661289</t>
+          <t>661036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>683636</t>
+          <t>682673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>700775</t>
+          <t>701788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>724062</t>
+          <t>724013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1370310</t>
+          <t>1370906</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1401409</t>
+          <t>1402712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58459</t>
+          <t>58458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>59006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67053</t>
+          <t>67562</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114792</t>
+          <t>114383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124422</t>
+          <t>124466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>446437</t>
+          <t>446523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>461501</t>
+          <t>461653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>468550</t>
+          <t>467385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>481235</t>
+          <t>481059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>920340</t>
+          <t>920710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>938974</t>
+          <t>939550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,82 +5770,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>7205</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>13032</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>7205</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>3448</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>13336</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>156944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167873</t>
+          <t>167665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177755</t>
+          <t>177177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185254</t>
+          <t>185253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338576</t>
+          <t>338131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351624</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>665699</t>
+          <t>665910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>684384</t>
+          <t>683685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>713216</t>
+          <t>713081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>730234</t>
+          <t>729719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1384679</t>
+          <t>1384601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1411031</t>
+          <t>1409256</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>50281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54999</t>
+          <t>54022</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108771</t>
+          <t>107849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114933</t>
+          <t>115031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>44671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>433809</t>
+          <t>436106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>452619</t>
+          <t>452831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>476605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>506821</t>
+          <t>506806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>924538</t>
+          <t>923187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>955595</t>
+          <t>956201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,47 +7938,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2405</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5539</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137392</t>
+          <t>137969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146517</t>
+          <t>146574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174308</t>
+          <t>173944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181339</t>
+          <t>181198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314743</t>
+          <t>314999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326290</t>
+          <t>326342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>629621</t>
+          <t>631369</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650162</t>
+          <t>649674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>715563</t>
+          <t>714587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>745770</t>
+          <t>745205</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1354180</t>
+          <t>1357270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1391305</t>
+          <t>1392830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP32-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3869</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7826</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2656</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6693</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3140</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7215</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>3,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8957</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>79496</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74461</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82912</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83857</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>78421</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>87296</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>78672</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>87331</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>92,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>86,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>79496</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74260</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82864</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156731</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168349</t>
+          <t>168068</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18400</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12124</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26681</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17320</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11644</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24973</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>24905</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18400</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12622</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26392</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22908</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31376</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19594</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13534</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28348</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13537</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>27891</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>4,73%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22908</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>15341</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>31874</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53315</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>433696</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>422112</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>442556</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>571</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>377339</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>367145</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>386012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>367094</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>385889</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>433696</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>421942</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>443230</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>797273</t>
+          <t>796712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>823243</t>
+          <t>824067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475003</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475003</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>414253</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>414253</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>414253</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475003</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>475003</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>475003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12139</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7475</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19306</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10298</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6067</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17132</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16408</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12139</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7429</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18378</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13378</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8502</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9732</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5720</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16571</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15443</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13378</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20453</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132620</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123976</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139641</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>154036</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>145769</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159768</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146688</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>160352</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132620</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>124304</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>139003</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275352</t>
+          <t>275655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296966</t>
+          <t>295897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,74 +2091,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33195</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24873</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42951</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>31487</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23854</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41538</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23888</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>41595</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>6,12%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33195</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42657</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>96</t>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>53400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>79277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40979</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31844</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52032</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>32466</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24437</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42420</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24328</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42905</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40979</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>31907</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>51429</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61271</t>
+          <t>60865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87948</t>
+          <t>86904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>645811</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>632118</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>658744</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>87,8%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>922</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>615234</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>601674</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>626517</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>601921</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>626351</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>90,58%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>645811</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>632812</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>658334</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>89,7%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1243199</t>
+          <t>1242791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1278122</t>
+          <t>1278098</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>719985</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>719985</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>719985</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>679187</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>679187</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>679187</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>719985</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>719985</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>719985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4045</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6137</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2693</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11504</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11797</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4045</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8950</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7789</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2323</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6861</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6579</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3419</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78728</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>72221</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82469</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83910</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>77679</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>88080</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>77669</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>88289</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>90,84%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>84,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>78728</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>72467</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82477</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154285</t>
+          <t>154456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168240</t>
+          <t>168207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17080</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26460</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14519</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8586</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22691</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22546</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17080</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9237</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25976</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43760</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3347,74 +3347,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5455</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10901</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>7674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4135</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>13707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13690</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5455</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>10721</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>19</t>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>20146</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>471911</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>460926</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>478598</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>430017</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>420237</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>437447</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>420885</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>437563</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>95,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>471911</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>462104</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>479784</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>888435</t>
+          <t>889131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>912817</t>
+          <t>912895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6611</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12485</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5282</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10938</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6611</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2907</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13341</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1979</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2438</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163180</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>156647</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167203</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>159551</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>153775</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163140</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153480</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>163180</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156415</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>167624</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313008</t>
+          <t>314144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328780</t>
+          <t>328201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27735</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18542</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39369</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25937</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17313</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36547</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17454</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37515</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,65%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27735</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18866</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>39979</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68784</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4264,67 +4264,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>11312</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6784</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17643</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>11976</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7213</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18702</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7258</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19102</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11312</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6950</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>17326</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>713819</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700339</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>723730</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>94,81%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>979</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>673478</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>661036</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>682673</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>661567</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>683388</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>94,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>713819</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>701788</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>724013</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1370906</t>
+          <t>1370580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1402712</t>
+          <t>1401197</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2794</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7340</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7560</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3820</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8655</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4946,107 +4946,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4384</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3603</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64081</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58678</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66959</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56584</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52038</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>58458</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>51818</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>58449</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64081</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>59006</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67562</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114383</t>
+          <t>114394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124466</t>
+          <t>124514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7478</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14243</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9134</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4671</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15558</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16654</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7478</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13580</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5260</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9765</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>7604</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3815</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>13955</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14255</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5260</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9816</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>475997</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>468553</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>481636</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>455552</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>446523</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>461653</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>446438</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>461778</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>96,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>475997</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>467385</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>481059</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>920710</t>
+          <t>920543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>939550</t>
+          <t>939670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4733</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10431</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9896</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7234</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6435</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4182</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8347</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8488</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>182596</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>177518</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>185221</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>163788</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156944</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167665</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158102</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167772</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>182596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>177177</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>185253</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338131</t>
+          <t>339760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351291</t>
+          <t>351077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186782</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186782</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186782</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186782</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186782</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13771</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8393</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22727</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>16660</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10262</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24565</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25502</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13771</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7932</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21833</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42741</t>
+          <t>41417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14346</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>11786</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7249</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18074</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19010</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3794</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13180</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722674</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>713176</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>729247</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>675924</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665910</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>683685</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>665380</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>683848</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>95,96%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722674</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>713081</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>729719</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1384601</t>
+          <t>1385544</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1409256</t>
+          <t>1410048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4397</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -7001,107 +7001,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1484</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54756</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50628</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56227</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53103</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>50281</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54192</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>44246</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112794</t>
+          <t>99002</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>94746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115031</t>
+          <t>101379</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11582</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18424</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19690</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44671</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9402</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -7570,107 +7570,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>461000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>452976</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>466985</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>446930</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>436106</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>452831</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>497575</t>
+          <t>420863</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>476605</t>
+          <t>414997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>506806</t>
+          <t>424996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>881863</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>872615</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>889616</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>96,31%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>944504</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>923187</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>956201</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>975123</t>
+          <t>906064</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975123</t>
+          <t>906064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>975123</t>
+          <t>906064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2539</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7035</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8313</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2793</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163820</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>159148</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166355</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>143419</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137969</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146574</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>178743</t>
+          <t>143438</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173944</t>
+          <t>138828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181198</t>
+          <t>146407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>322163</t>
+          <t>307258</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314999</t>
+          <t>301113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326342</t>
+          <t>311152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15849</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10292</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24585</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11860</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6798</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25538</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,22 +8331,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -8369,107 +8369,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7420</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12803</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3451</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>12826</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>7657</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>20185</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5946</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3007</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>11505</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>13366</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>8174</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>679577</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>670336</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686173</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>643452</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>631369</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>649674</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>736008</t>
+          <t>608548</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>714587</t>
+          <t>601229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>745205</t>
+          <t>614716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1379461</t>
+          <t>1288124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1357270</t>
+          <t>1277262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1392830</t>
+          <t>1297834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1424705</t>
+          <t>1327949</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1424705</t>
+          <t>1327949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1424705</t>
+          <t>1327949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
